--- a/Morphometrics/morphology_by_species_for_taxonomic_treatment.xlsx
+++ b/Morphometrics/morphology_by_species_for_taxonomic_treatment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/GitHub/Heuchera-americana-group-species-manuscript/Morphometrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6E7F2DD9-B9F0-794C-B4FC-83119DE48489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0622CC0-C169-BE43-AEC1-758DEB6C4A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16420" activeTab="3" xr2:uid="{37DF62A1-309C-2E49-B246-2BDE6342D869}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16420" xr2:uid="{37DF62A1-309C-2E49-B246-2BDE6342D869}"/>
   </bookViews>
   <sheets>
     <sheet name="Median &amp; Ranges" sheetId="10" r:id="rId1"/>
@@ -24,12 +24,25 @@
     <sheet name="Brevipetala" sheetId="3" r:id="rId9"/>
     <sheet name="Americana" sheetId="2" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>

--- a/Morphometrics/morphology_by_species_for_taxonomic_treatment.xlsx
+++ b/Morphometrics/morphology_by_species_for_taxonomic_treatment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/GitHub/Heuchera-americana-group-species-manuscript/Morphometrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0622CC0-C169-BE43-AEC1-758DEB6C4A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316664A5-E8F8-4C45-8E35-1648E4DE5BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16420" xr2:uid="{37DF62A1-309C-2E49-B246-2BDE6342D869}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{37DF62A1-309C-2E49-B246-2BDE6342D869}"/>
   </bookViews>
   <sheets>
     <sheet name="Median &amp; Ranges" sheetId="10" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3715" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3750" uniqueCount="246">
   <si>
     <t>Species</t>
   </si>
@@ -792,12 +792,45 @@
       <t>(absolute min) min–max (absolute max) mm</t>
     </r>
   </si>
+  <si>
+    <t>Petiole_length</t>
+  </si>
+  <si>
+    <t>Leaf_width</t>
+  </si>
+  <si>
+    <t>Leaf_length</t>
+  </si>
+  <si>
+    <t>Capsule_width</t>
+  </si>
+  <si>
+    <t>Capsule_length</t>
+  </si>
+  <si>
+    <t>Cymule_flower_counts</t>
+  </si>
+  <si>
+    <t>Cymule_lengths</t>
+  </si>
+  <si>
+    <t>free_sepal_length</t>
+  </si>
+  <si>
+    <t>hypanthia_width_at_sepal_sinus</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Whole_Cymule_lengths</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -957,6 +990,12 @@
       <color rgb="FFFFFF00"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="41">
@@ -1734,24 +1773,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3386285D-3D13-374B-A6F3-51FAF5916581}">
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:Y102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="38" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1800,8 +1848,35 @@
       <c r="P1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q1" t="s">
+        <v>235</v>
+      </c>
+      <c r="R1" t="s">
+        <v>236</v>
+      </c>
+      <c r="S1" t="s">
+        <v>237</v>
+      </c>
+      <c r="T1" t="s">
+        <v>238</v>
+      </c>
+      <c r="U1" t="s">
+        <v>239</v>
+      </c>
+      <c r="V1" t="s">
+        <v>240</v>
+      </c>
+      <c r="W1" t="s">
+        <v>245</v>
+      </c>
+      <c r="X1" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>216</v>
       </c>
@@ -1865,7 +1940,7 @@
         <v>575.44650000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>216</v>
       </c>
@@ -1929,7 +2004,7 @@
         <v>687.77549999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>216</v>
       </c>
@@ -1993,7 +2068,7 @@
         <v>768.61675000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>216</v>
       </c>
@@ -2057,7 +2132,7 @@
         <v>193.17025000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>216</v>
       </c>
@@ -2121,7 +2196,7 @@
         <v>285.691125</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>216</v>
       </c>
@@ -2185,7 +2260,7 @@
         <v>1058.3721250000001</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>216</v>
       </c>
@@ -2249,7 +2324,7 @@
         <v>436.43</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>216</v>
       </c>
@@ -2313,7 +2388,7 @@
         <v>945.75800000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="8" customFormat="1" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" s="8" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>216</v>
       </c>
@@ -2377,7 +2452,7 @@
         <v>() 436.43–945.758 () mm</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>198</v>
       </c>
@@ -2441,7 +2516,7 @@
         <v>581.36725000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>199</v>
       </c>
@@ -2505,7 +2580,7 @@
         <v>694.71199999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>200</v>
       </c>
@@ -2569,7 +2644,7 @@
         <v>783.85524999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>201</v>
       </c>
@@ -2633,7 +2708,7 @@
         <v>202.48799999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>202</v>
       </c>
@@ -2697,7 +2772,7 @@
         <v>277.6352500000001</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>203</v>
       </c>
@@ -2761,7 +2836,7 @@
         <v>1087.5872499999998</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>205</v>
       </c>
@@ -2825,7 +2900,7 @@
         <v>238.65199999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>204</v>
       </c>
@@ -2833,7 +2908,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="19" spans="1:16" s="7" customFormat="1" ht="17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" s="7" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>206</v>
       </c>
@@ -2897,7 +2972,7 @@
         <v>(238.652) 322.12–1012.704 (1012.704) mm</v>
       </c>
     </row>
-    <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>207</v>
       </c>
@@ -2961,7 +3036,7 @@
         <v>599.27800000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>208</v>
       </c>
@@ -3025,7 +3100,7 @@
         <v>673.39300000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>209</v>
       </c>
@@ -3089,7 +3164,7 @@
         <v>816.57600000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>210</v>
       </c>
@@ -3153,7 +3228,7 @@
         <v>217.298</v>
       </c>
     </row>
-    <row r="24" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>211</v>
       </c>
@@ -3217,7 +3292,7 @@
         <v>273.33100000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>212</v>
       </c>
@@ -3281,7 +3356,7 @@
         <v>1142.5230000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>213</v>
       </c>
@@ -3345,7 +3420,7 @@
         <v>481.68799999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>214</v>
       </c>
@@ -3409,7 +3484,7 @@
         <v>961.61900000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:16" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>215</v>
       </c>
@@ -3472,8 +3547,36 @@
         <f>"(" &amp; IF(MIN(Calycosa!R$2:R$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)),MIN(Calycosa!R$2:R$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!R$2:R$1000, Calycosa!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)), Calycosa!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!R$2:R$1000, Calycosa!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)), Calycosa!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!R$2:R$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)),MAX(Calycosa!R$2:R$1000),"") &amp; ") mm"</f>
         <v>() 481.688–961.619 () mm</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q28" s="6" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!S$2:S$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,1)),MIN(Calycosa!S$2:S$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!S$2:S$1000, Calycosa!S$2:S$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,1)), Calycosa!S$2:S$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!S$2:S$1000, Calycosa!S$2:S$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,1)), Calycosa!S$2:S$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!S$2:S$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Calycosa!S$2:S$1000,1)),MAX(Calycosa!S$2:S$1000),"") &amp; ") mm"</f>
+        <v>() 56.693–137.543 () mm</v>
+      </c>
+      <c r="R28" s="6" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!T$2:T$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,1)),MIN(Calycosa!T$2:T$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!T$2:T$1000, Calycosa!T$2:T$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,1)), Calycosa!T$2:T$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!T$2:T$1000, Calycosa!T$2:T$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,1)), Calycosa!T$2:T$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!T$2:T$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Calycosa!T$2:T$1000,1)),MAX(Calycosa!T$2:T$1000),"") &amp; ") mm"</f>
+        <v>() 29.45–63.927 () mm</v>
+      </c>
+      <c r="S28" s="6" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!U$2:U$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,1)),MIN(Calycosa!U$2:U$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!U$2:U$1000, Calycosa!U$2:U$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,1)), Calycosa!U$2:U$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!U$2:U$1000, Calycosa!U$2:U$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,1)), Calycosa!U$2:U$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!U$2:U$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Calycosa!U$2:U$1000,1)),MAX(Calycosa!U$2:U$1000),"") &amp; ") mm"</f>
+        <v>(32.406) 44.714–62.816 (72.577) mm</v>
+      </c>
+      <c r="T28" s="6" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!V$2:V$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,1)),MIN(Calycosa!V$2:V$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!V$2:V$1000, Calycosa!V$2:V$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,1)), Calycosa!V$2:V$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!V$2:V$1000, Calycosa!V$2:V$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,1)), Calycosa!V$2:V$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!V$2:V$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Calycosa!V$2:V$1000,1)),MAX(Calycosa!V$2:V$1000),"") &amp; ") mm"</f>
+        <v>() 2.635–4.068 (4.858) mm</v>
+      </c>
+      <c r="U28" s="6" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!W$2:W$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,1)),MIN(Calycosa!W$2:W$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!W$2:W$1000, Calycosa!W$2:W$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,1)), Calycosa!W$2:W$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!W$2:W$1000, Calycosa!W$2:W$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,1)), Calycosa!W$2:W$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!W$2:W$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Calycosa!W$2:W$1000,1)),MAX(Calycosa!W$2:W$1000),"") &amp; ") mm"</f>
+        <v>() 3.905–5.235 (6.58) mm</v>
+      </c>
+      <c r="V28" s="6" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!X$2:X$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,1)),MIN(Calycosa!X$2:X$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!X$2:X$1000, Calycosa!X$2:X$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,1)), Calycosa!X$2:X$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!X$2:X$1000, Calycosa!X$2:X$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,1)), Calycosa!X$2:X$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!X$2:X$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Calycosa!X$2:X$1000,1)),MAX(Calycosa!X$2:X$1000),"") &amp; ") mm"</f>
+        <v>() 4–7 (8) mm</v>
+      </c>
+      <c r="W28" s="6" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!Y$2:Y$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,1)),MIN(Calycosa!Y$2:Y$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!Y$2:Y$1000, Calycosa!Y$2:Y$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,1)), Calycosa!Y$2:Y$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!Y$2:Y$1000, Calycosa!Y$2:Y$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,1)), Calycosa!Y$2:Y$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!Y$2:Y$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Y$2:Y$1000,1)),MAX(Calycosa!Y$2:Y$1000),"") &amp; ") mm"</f>
+        <v>() 21.811–42.375 () mm</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>99</v>
       </c>
@@ -3537,7 +3640,7 @@
         <v>71.174000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>99</v>
       </c>
@@ -3601,7 +3704,7 @@
         <v>75.647999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>99</v>
       </c>
@@ -3665,7 +3768,7 @@
         <v>80.122</v>
       </c>
     </row>
-    <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>99</v>
       </c>
@@ -3729,7 +3832,7 @@
         <v>8.9479999999999933</v>
       </c>
     </row>
-    <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>99</v>
       </c>
@@ -3793,7 +3896,7 @@
         <v>57.752000000000017</v>
       </c>
     </row>
-    <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>99</v>
       </c>
@@ -3857,7 +3960,7 @@
         <v>93.543999999999983</v>
       </c>
     </row>
-    <row r="35" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>99</v>
       </c>
@@ -3921,7 +4024,7 @@
         <v>66.7</v>
       </c>
     </row>
-    <row r="36" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>99</v>
       </c>
@@ -3985,7 +4088,7 @@
         <v>84.596000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:16" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>99</v>
       </c>
@@ -4048,8 +4151,44 @@
         <f>"(" &amp; IF(MIN(Fumosimontana!R$2:R$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)),MIN(Fumosimontana!R$2:R$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!R$2:R$1000, Fumosimontana!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)), Fumosimontana!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!R$2:R$1000, Fumosimontana!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)), Fumosimontana!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!R$2:R$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)),MAX(Fumosimontana!R$2:R$1000),"") &amp; ") mm"</f>
         <v>() 66.7–84.596 () mm</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q37" s="5" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!S$2:S$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)),MIN(Fumosimontana!S$2:S$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!S$2:S$1000, Fumosimontana!S$2:S$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)), Fumosimontana!S$2:S$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!S$2:S$1000, Fumosimontana!S$2:S$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)), Fumosimontana!S$2:S$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!S$2:S$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)),MAX(Fumosimontana!S$2:S$1000),"") &amp; ") mm"</f>
+        <v>() 58.049–179.083 () mm</v>
+      </c>
+      <c r="R37" s="5" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!T$2:T$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,1)),MIN(Fumosimontana!T$2:T$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!T$2:T$1000, Fumosimontana!T$2:T$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,1)), Fumosimontana!T$2:T$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!T$2:T$1000, Fumosimontana!T$2:T$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,1)), Fumosimontana!T$2:T$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!T$2:T$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!T$2:T$1000,1)),MAX(Fumosimontana!T$2:T$1000),"") &amp; ") mm"</f>
+        <v>() 48.738–78.959 () mm</v>
+      </c>
+      <c r="S37" s="5" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!U$2:U$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,1)),MIN(Fumosimontana!U$2:U$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!U$2:U$1000, Fumosimontana!U$2:U$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,1)), Fumosimontana!U$2:U$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!U$2:U$1000, Fumosimontana!U$2:U$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,1)), Fumosimontana!U$2:U$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!U$2:U$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!U$2:U$1000,1)),MAX(Fumosimontana!U$2:U$1000),"") &amp; ") mm"</f>
+        <v>() 54.192–92.134 () mm</v>
+      </c>
+      <c r="T37" s="5" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!V$2:V$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,1)),MIN(Fumosimontana!V$2:V$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!V$2:V$1000, Fumosimontana!V$2:V$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,1)), Fumosimontana!V$2:V$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!V$2:V$1000, Fumosimontana!V$2:V$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,1)), Fumosimontana!V$2:V$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!V$2:V$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!V$2:V$1000,1)),MAX(Fumosimontana!V$2:V$1000),"") &amp; ") mm"</f>
+        <v>() 3.281–3.88 () mm</v>
+      </c>
+      <c r="U37" s="5" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!W$2:W$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,1)),MIN(Fumosimontana!W$2:W$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!W$2:W$1000, Fumosimontana!W$2:W$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,1)), Fumosimontana!W$2:W$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!W$2:W$1000, Fumosimontana!W$2:W$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,1)), Fumosimontana!W$2:W$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!W$2:W$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!W$2:W$1000,1)),MAX(Fumosimontana!W$2:W$1000),"") &amp; ") mm"</f>
+        <v>() 4.9–5.996 () mm</v>
+      </c>
+      <c r="V37" s="5" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!X$2:X$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,1)),MIN(Fumosimontana!X$2:X$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!X$2:X$1000, Fumosimontana!X$2:X$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,1)), Fumosimontana!X$2:X$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!X$2:X$1000, Fumosimontana!X$2:X$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,1)), Fumosimontana!X$2:X$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!X$2:X$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!X$2:X$1000,1)),MAX(Fumosimontana!X$2:X$1000),"") &amp; ") mm"</f>
+        <v>() 4–12 () mm</v>
+      </c>
+      <c r="W37" s="5" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!Y$2:Y$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,1)),MIN(Fumosimontana!Y$2:Y$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!Y$2:Y$1000, Fumosimontana!Y$2:Y$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,1)), Fumosimontana!Y$2:Y$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!Y$2:Y$1000, Fumosimontana!Y$2:Y$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,1)), Fumosimontana!Y$2:Y$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!Y$2:Y$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Y$2:Y$1000,1)),MAX(Fumosimontana!Y$2:Y$1000),"") &amp; ") mm"</f>
+        <v>() 23.822–43.368 () mm</v>
+      </c>
+      <c r="X37" s="5" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!Z$2:Z$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,1)),MIN(Fumosimontana!Z$2:Z$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!Z$2:Z$1000, Fumosimontana!Z$2:Z$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,1)), Fumosimontana!Z$2:Z$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!Z$2:Z$1000, Fumosimontana!Z$2:Z$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,1)), Fumosimontana!Z$2:Z$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!Z$2:Z$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Z$2:Z$1000,1)),MAX(Fumosimontana!Z$2:Z$1000),"") &amp; ") mm"</f>
+        <v>(0.826) 1.05–1.298 (1.775) mm</v>
+      </c>
+      <c r="Y37" s="5" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!AA$2:AA$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,1)),MIN(Fumosimontana!AA$2:AA$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!AA$2:AA$1000, Fumosimontana!AA$2:AA$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,1)), Fumosimontana!AA$2:AA$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!AA$2:AA$1000, Fumosimontana!AA$2:AA$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,1)), Fumosimontana!AA$2:AA$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!AA$2:AA$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!AA$2:AA$1000,1)),MAX(Fumosimontana!AA$2:AA$1000),"") &amp; ") mm"</f>
+        <v>() 1.771–3.88 () mm</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>104</v>
       </c>
@@ -4113,7 +4252,7 @@
         <v>519.05799999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>104</v>
       </c>
@@ -4177,7 +4316,7 @@
         <v>657.42599999999993</v>
       </c>
     </row>
-    <row r="40" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>104</v>
       </c>
@@ -4241,7 +4380,7 @@
         <v>751.36474999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>104</v>
       </c>
@@ -4305,7 +4444,7 @@
         <v>232.30674999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>104</v>
       </c>
@@ -4369,7 +4508,7 @@
         <v>170.59787500000004</v>
       </c>
     </row>
-    <row r="43" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>104</v>
       </c>
@@ -4433,7 +4572,7 @@
         <v>1099.8248749999998</v>
       </c>
     </row>
-    <row r="44" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>104</v>
       </c>
@@ -4497,7 +4636,7 @@
         <v>380.75099999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>104</v>
       </c>
@@ -4561,7 +4700,7 @@
         <v>874.66700000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:16" s="3" customFormat="1" ht="17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" s="3" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>104</v>
       </c>
@@ -4625,7 +4764,7 @@
         <v>() 380.751–874.667 () mm</v>
       </c>
     </row>
-    <row r="47" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>127</v>
       </c>
@@ -4689,7 +4828,7 @@
         <v>374.44550000000004</v>
       </c>
     </row>
-    <row r="48" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>127</v>
       </c>
@@ -40550,10 +40689,39 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2E0072-4AB0-F041-AF4E-7CDA50AF3C1E}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:AH20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.1640625" customWidth="1"/>
+    <col min="20" max="20" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.83203125" customWidth="1"/>
+    <col min="27" max="27" width="29.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -40608,8 +40776,53 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S1" t="s">
+        <v>235</v>
+      </c>
+      <c r="T1" t="s">
+        <v>236</v>
+      </c>
+      <c r="U1" t="s">
+        <v>237</v>
+      </c>
+      <c r="V1" t="s">
+        <v>238</v>
+      </c>
+      <c r="W1" t="s">
+        <v>239</v>
+      </c>
+      <c r="X1" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC1">
+        <v>4</v>
+      </c>
+      <c r="AD1">
+        <v>11.169</v>
+      </c>
+      <c r="AE1">
+        <v>111.116</v>
+      </c>
+      <c r="AF1">
+        <v>0.878</v>
+      </c>
+      <c r="AG1">
+        <v>251.81299999999999</v>
+      </c>
+      <c r="AH1">
+        <v>116.065</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>99</v>
       </c>
@@ -40662,8 +40875,47 @@
         <v>35.14</v>
       </c>
       <c r="R2" s="1"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S2">
+        <v>99.671999999999997</v>
+      </c>
+      <c r="T2">
+        <v>62.081000000000003</v>
+      </c>
+      <c r="U2">
+        <v>79.552000000000007</v>
+      </c>
+      <c r="X2">
+        <v>5</v>
+      </c>
+      <c r="Y2">
+        <v>30.966999999999999</v>
+      </c>
+      <c r="Z2">
+        <v>1.141</v>
+      </c>
+      <c r="AA2">
+        <v>3.798</v>
+      </c>
+      <c r="AC2">
+        <v>5</v>
+      </c>
+      <c r="AD2">
+        <v>5.5839999999999996</v>
+      </c>
+      <c r="AE2">
+        <v>140.286</v>
+      </c>
+      <c r="AF2">
+        <v>13.148999999999999</v>
+      </c>
+      <c r="AG2">
+        <v>254.10300000000001</v>
+      </c>
+      <c r="AH2">
+        <v>58.048999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>99</v>
       </c>
@@ -40716,8 +40968,29 @@
         <v>25.54</v>
       </c>
       <c r="R3" s="1"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S3">
+        <v>101.92</v>
+      </c>
+      <c r="T3">
+        <v>48.738</v>
+      </c>
+      <c r="U3">
+        <v>67.926000000000002</v>
+      </c>
+      <c r="X3">
+        <v>5</v>
+      </c>
+      <c r="Y3">
+        <v>29.145</v>
+      </c>
+      <c r="Z3">
+        <v>1.085</v>
+      </c>
+      <c r="AA3">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>99</v>
       </c>
@@ -40770,8 +41043,29 @@
         <v>25.84</v>
       </c>
       <c r="R4" s="1"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S4">
+        <v>99.290999999999997</v>
+      </c>
+      <c r="T4">
+        <v>71.576999999999998</v>
+      </c>
+      <c r="U4">
+        <v>54.192</v>
+      </c>
+      <c r="X4">
+        <v>5</v>
+      </c>
+      <c r="Y4">
+        <v>23.821999999999999</v>
+      </c>
+      <c r="Z4">
+        <v>1.069</v>
+      </c>
+      <c r="AA4">
+        <v>3.6379999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>99</v>
       </c>
@@ -40826,8 +41120,35 @@
       <c r="R5" s="1">
         <v>66.7</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S5">
+        <v>164.863</v>
+      </c>
+      <c r="T5" s="1">
+        <v>73.947999999999993</v>
+      </c>
+      <c r="U5">
+        <v>80.521000000000001</v>
+      </c>
+      <c r="V5">
+        <v>3.8260000000000001</v>
+      </c>
+      <c r="W5">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X5">
+        <v>5</v>
+      </c>
+      <c r="Y5">
+        <v>43.368000000000002</v>
+      </c>
+      <c r="Z5">
+        <v>1.1379999999999999</v>
+      </c>
+      <c r="AA5">
+        <v>2.556</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>99</v>
       </c>
@@ -40880,8 +41201,32 @@
         <v>19.850000000000001</v>
       </c>
       <c r="R6" s="1"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S6">
+        <v>179.083</v>
+      </c>
+      <c r="U6">
+        <v>84.117999999999995</v>
+      </c>
+      <c r="V6">
+        <v>3.2810000000000001</v>
+      </c>
+      <c r="W6">
+        <v>5.9960000000000004</v>
+      </c>
+      <c r="X6">
+        <v>4</v>
+      </c>
+      <c r="Y6">
+        <v>34.433</v>
+      </c>
+      <c r="Z6">
+        <v>1.129</v>
+      </c>
+      <c r="AA6">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>99</v>
       </c>
@@ -40934,8 +41279,29 @@
         <v>15.28</v>
       </c>
       <c r="R7" s="1"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7">
+        <v>132.63999999999999</v>
+      </c>
+      <c r="V7">
+        <v>3.57</v>
+      </c>
+      <c r="W7">
+        <v>5.2949999999999999</v>
+      </c>
+      <c r="X7">
+        <v>7</v>
+      </c>
+      <c r="Y7">
+        <v>39.951000000000001</v>
+      </c>
+      <c r="Z7">
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="AA7">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>99</v>
       </c>
@@ -40988,8 +41354,32 @@
         <v>8.34</v>
       </c>
       <c r="R8" s="1"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8">
+        <v>143.60499999999999</v>
+      </c>
+      <c r="T8">
+        <v>77.528000000000006</v>
+      </c>
+      <c r="U8">
+        <v>92.134</v>
+      </c>
+      <c r="V8">
+        <v>3.88</v>
+      </c>
+      <c r="W8">
+        <v>4.9189999999999996</v>
+      </c>
+      <c r="Y8">
+        <v>28.861999999999998</v>
+      </c>
+      <c r="Z8">
+        <v>1.2869999999999999</v>
+      </c>
+      <c r="AA8">
+        <v>1.7709999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>99</v>
       </c>
@@ -41042,8 +41432,32 @@
         <v>21.47</v>
       </c>
       <c r="R9" s="1"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9">
+        <v>78.703999999999994</v>
+      </c>
+      <c r="T9">
+        <v>67.686000000000007</v>
+      </c>
+      <c r="U9">
+        <v>80.063000000000002</v>
+      </c>
+      <c r="V9">
+        <v>3.5459999999999998</v>
+      </c>
+      <c r="W9">
+        <v>5.6740000000000004</v>
+      </c>
+      <c r="Y9">
+        <v>35.034999999999997</v>
+      </c>
+      <c r="Z9">
+        <v>1.1519999999999999</v>
+      </c>
+      <c r="AA9">
+        <v>3.0710000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
@@ -41096,8 +41510,32 @@
         <v>17.63</v>
       </c>
       <c r="R10" s="1"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10">
+        <v>144.81299999999999</v>
+      </c>
+      <c r="T10">
+        <v>78.959000000000003</v>
+      </c>
+      <c r="U10">
+        <v>80.363</v>
+      </c>
+      <c r="V10">
+        <v>3.4780000000000002</v>
+      </c>
+      <c r="W10">
+        <v>5.5430000000000001</v>
+      </c>
+      <c r="Y10">
+        <v>33.002000000000002</v>
+      </c>
+      <c r="Z10">
+        <v>1.05</v>
+      </c>
+      <c r="AA10">
+        <v>3.0430000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>99</v>
       </c>
@@ -41152,8 +41590,29 @@
       <c r="R11" s="1">
         <v>84.596000000000004</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11">
+        <v>116.065</v>
+      </c>
+      <c r="T11">
+        <v>57.344000000000001</v>
+      </c>
+      <c r="U11">
+        <v>65.245999999999995</v>
+      </c>
+      <c r="X11">
+        <v>9</v>
+      </c>
+      <c r="Y11">
+        <v>39.703000000000003</v>
+      </c>
+      <c r="Z11">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="AA11">
+        <v>3.7309999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>99</v>
       </c>
@@ -41206,8 +41665,29 @@
         <v>20.420000000000002</v>
       </c>
       <c r="R12" s="1"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12">
+        <v>58.048999999999999</v>
+      </c>
+      <c r="T12">
+        <v>49.076999999999998</v>
+      </c>
+      <c r="U12">
+        <v>65.676000000000002</v>
+      </c>
+      <c r="X12">
+        <v>12</v>
+      </c>
+      <c r="Y12">
+        <v>36.576000000000001</v>
+      </c>
+      <c r="Z12">
+        <v>0.82599999999999996</v>
+      </c>
+      <c r="AA12">
+        <v>3.2440000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>99</v>
       </c>
@@ -41260,18 +41740,84 @@
         <v>20.27</v>
       </c>
       <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13">
+        <v>53.551000000000002</v>
+      </c>
+      <c r="U13">
+        <v>79.126999999999995</v>
+      </c>
+      <c r="X13">
+        <v>11</v>
+      </c>
+      <c r="Y13">
+        <v>33.408999999999999</v>
+      </c>
+      <c r="Z13">
+        <v>1.298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4926DEDF-AD09-6246-A1FF-F797BAB63D4D}">
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="22" max="22" width="14.33203125" customWidth="1"/>
+    <col min="23" max="23" width="15.83203125" customWidth="1"/>
+    <col min="24" max="24" width="19.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -41326,8 +41872,29 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S1" t="s">
+        <v>235</v>
+      </c>
+      <c r="T1" t="s">
+        <v>236</v>
+      </c>
+      <c r="U1" t="s">
+        <v>237</v>
+      </c>
+      <c r="V1" t="s">
+        <v>238</v>
+      </c>
+      <c r="W1" t="s">
+        <v>239</v>
+      </c>
+      <c r="X1" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>85</v>
       </c>
@@ -41382,8 +41949,29 @@
       <c r="R2" s="1">
         <v>589.41800000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S2">
+        <v>123.88</v>
+      </c>
+      <c r="T2">
+        <v>38.86</v>
+      </c>
+      <c r="U2">
+        <v>72.576999999999998</v>
+      </c>
+      <c r="V2">
+        <v>4.8579999999999997</v>
+      </c>
+      <c r="W2">
+        <v>4.609</v>
+      </c>
+      <c r="X2">
+        <v>5</v>
+      </c>
+      <c r="Y2">
+        <v>37.045000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>85</v>
       </c>
@@ -41436,8 +42024,29 @@
         <v>27.811</v>
       </c>
       <c r="R3" s="1"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S3">
+        <v>133.548</v>
+      </c>
+      <c r="T3">
+        <v>29.45</v>
+      </c>
+      <c r="U3">
+        <v>51.713999999999999</v>
+      </c>
+      <c r="V3">
+        <v>4.0679999999999996</v>
+      </c>
+      <c r="W3">
+        <v>5.0990000000000002</v>
+      </c>
+      <c r="X3">
+        <v>7</v>
+      </c>
+      <c r="Y3">
+        <v>35.637</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>85</v>
       </c>
@@ -41490,8 +42099,29 @@
         <v>24.45</v>
       </c>
       <c r="R4" s="1"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S4">
+        <v>114.708</v>
+      </c>
+      <c r="T4">
+        <v>63.927</v>
+      </c>
+      <c r="U4">
+        <v>48.795999999999999</v>
+      </c>
+      <c r="V4">
+        <v>3.512</v>
+      </c>
+      <c r="W4">
+        <v>6.58</v>
+      </c>
+      <c r="X4">
+        <v>5</v>
+      </c>
+      <c r="Y4">
+        <v>42.375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>85</v>
       </c>
@@ -41546,8 +42176,29 @@
       <c r="R5" s="1">
         <v>776.40599999999995</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S5">
+        <v>128.83000000000001</v>
+      </c>
+      <c r="T5">
+        <v>43.468000000000004</v>
+      </c>
+      <c r="U5">
+        <v>32.405999999999999</v>
+      </c>
+      <c r="V5">
+        <v>3.4420000000000002</v>
+      </c>
+      <c r="W5">
+        <v>4.8520000000000003</v>
+      </c>
+      <c r="X5">
+        <v>6</v>
+      </c>
+      <c r="Y5">
+        <v>36.145000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
@@ -41602,8 +42253,29 @@
       <c r="R6" s="1">
         <v>609.13800000000003</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S6">
+        <v>101.84</v>
+      </c>
+      <c r="T6">
+        <v>43.662999999999997</v>
+      </c>
+      <c r="U6">
+        <v>47.725000000000001</v>
+      </c>
+      <c r="V6">
+        <v>3.5630000000000002</v>
+      </c>
+      <c r="W6">
+        <v>4.2439999999999998</v>
+      </c>
+      <c r="X6">
+        <v>5</v>
+      </c>
+      <c r="Y6">
+        <v>28.108000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>85</v>
       </c>
@@ -41656,8 +42328,29 @@
         <v>16.477</v>
       </c>
       <c r="R7" s="1"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7">
+        <v>137.54300000000001</v>
+      </c>
+      <c r="T7">
+        <v>46.600999999999999</v>
+      </c>
+      <c r="U7">
+        <v>49.878999999999998</v>
+      </c>
+      <c r="V7">
+        <v>3.2879999999999998</v>
+      </c>
+      <c r="W7">
+        <v>5.2350000000000003</v>
+      </c>
+      <c r="X7">
+        <v>4</v>
+      </c>
+      <c r="Y7">
+        <v>29.341000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>85</v>
       </c>
@@ -41712,8 +42405,29 @@
       <c r="R8" s="1">
         <v>515.97799999999995</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8">
+        <v>105.72499999999999</v>
+      </c>
+      <c r="T8">
+        <v>41.960999999999999</v>
+      </c>
+      <c r="U8">
+        <v>44.713999999999999</v>
+      </c>
+      <c r="V8">
+        <v>2.6349999999999998</v>
+      </c>
+      <c r="W8">
+        <v>4.2629999999999999</v>
+      </c>
+      <c r="X8">
+        <v>6</v>
+      </c>
+      <c r="Y8">
+        <v>39.503</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>85</v>
       </c>
@@ -41768,8 +42482,29 @@
       <c r="R9" s="1">
         <v>481.68799999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9">
+        <v>87.843000000000004</v>
+      </c>
+      <c r="T9">
+        <v>59.15</v>
+      </c>
+      <c r="U9">
+        <v>52.442</v>
+      </c>
+      <c r="V9">
+        <v>2.8570000000000002</v>
+      </c>
+      <c r="W9">
+        <v>4.2430000000000003</v>
+      </c>
+      <c r="X9">
+        <v>4</v>
+      </c>
+      <c r="Y9">
+        <v>36.325000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>85</v>
       </c>
@@ -41822,8 +42557,29 @@
         <v>18.228999999999999</v>
       </c>
       <c r="R10" s="1"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10">
+        <v>84.408000000000001</v>
+      </c>
+      <c r="T10">
+        <v>57.776000000000003</v>
+      </c>
+      <c r="U10">
+        <v>54.442</v>
+      </c>
+      <c r="V10">
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="W10">
+        <v>5.1840000000000002</v>
+      </c>
+      <c r="X10">
+        <v>5</v>
+      </c>
+      <c r="Y10">
+        <v>30.920999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>85</v>
       </c>
@@ -41878,8 +42634,29 @@
       <c r="R11" s="1">
         <v>819.07</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11">
+        <v>85.465999999999994</v>
+      </c>
+      <c r="T11">
+        <v>48.692999999999998</v>
+      </c>
+      <c r="U11">
+        <v>57.545000000000002</v>
+      </c>
+      <c r="V11">
+        <v>3.2189999999999999</v>
+      </c>
+      <c r="W11">
+        <v>3.992</v>
+      </c>
+      <c r="X11">
+        <v>6</v>
+      </c>
+      <c r="Y11">
+        <v>33.162999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>85</v>
       </c>
@@ -41932,8 +42709,26 @@
         <v>12.718</v>
       </c>
       <c r="R12" s="1"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12">
+        <v>56.692999999999998</v>
+      </c>
+      <c r="U12">
+        <v>62.816000000000003</v>
+      </c>
+      <c r="V12">
+        <v>3.4550000000000001</v>
+      </c>
+      <c r="W12">
+        <v>3.9049999999999998</v>
+      </c>
+      <c r="X12">
+        <v>5</v>
+      </c>
+      <c r="Y12">
+        <v>26.835000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>85</v>
       </c>
@@ -41986,8 +42781,23 @@
         <v>11.782999999999999</v>
       </c>
       <c r="R13" s="1"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13">
+        <v>92.4</v>
+      </c>
+      <c r="V13">
+        <v>3.0819999999999999</v>
+      </c>
+      <c r="W13">
+        <v>4.2590000000000003</v>
+      </c>
+      <c r="X13">
+        <v>5</v>
+      </c>
+      <c r="Y13">
+        <v>21.811</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>85</v>
       </c>
@@ -42042,8 +42852,14 @@
       <c r="R14" s="1">
         <v>961.61900000000003</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14">
+        <v>82.787000000000006</v>
+      </c>
+      <c r="X14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>85</v>
       </c>
@@ -42098,8 +42914,11 @@
       <c r="R15" s="1">
         <v>655.32299999999998</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15">
+        <v>75.034000000000006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>85</v>
       </c>
@@ -42152,6 +42971,9 @@
         <v>21.521999999999998</v>
       </c>
       <c r="R16" s="1"/>
+      <c r="S16">
+        <v>132.53800000000001</v>
+      </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">

--- a/Morphometrics/morphology_by_species_for_taxonomic_treatment.xlsx
+++ b/Morphometrics/morphology_by_species_for_taxonomic_treatment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/GitHub/Heuchera-americana-group-species-manuscript/Morphometrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316664A5-E8F8-4C45-8E35-1648E4DE5BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C99458-6877-F84F-A55A-DF683E6EA8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{37DF62A1-309C-2E49-B246-2BDE6342D869}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" activeTab="6" xr2:uid="{37DF62A1-309C-2E49-B246-2BDE6342D869}"/>
   </bookViews>
   <sheets>
     <sheet name="Median &amp; Ranges" sheetId="10" r:id="rId1"/>
@@ -41,8 +41,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={8BCB5CE8-1748-AD4C-925E-502A7B2D320F}</author>
+  </authors>
+  <commentList>
+    <comment ref="R14" authorId="0" shapeId="0" xr:uid="{8BCB5CE8-1748-AD4C-925E-502A7B2D320F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    These are real min and max, I had a couple more measurements but lost by closing without saving. I am just reporting min max in paper</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3750" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3740" uniqueCount="245">
   <si>
     <t>Species</t>
   </si>
@@ -820,9 +838,6 @@
     <t>hypanthia_width_at_sepal_sinus</t>
   </si>
   <si>
-    <t>A4</t>
-  </si>
-  <si>
     <t>Whole_Cymule_lengths</t>
   </si>
 </sst>
@@ -830,7 +845,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -996,6 +1011,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="41">
@@ -1387,7 +1414,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1398,6 +1425,7 @@
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1454,6 +1482,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Engle-Wrye, Nicholas" id="{E8EA8297-45F8-AA47-8ABB-2B963EAC145A}" userId="S::nje59@msstate.edu::52028c67-32e2-4e20-832f-0f6e68e1bc05" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1771,6 +1805,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="R14" dT="2026-02-06T15:06:37.10" personId="{E8EA8297-45F8-AA47-8ABB-2B963EAC145A}" id="{8BCB5CE8-1748-AD4C-925E-502A7B2D320F}">
+    <text>These are real min and max, I had a couple more measurements but lost by closing without saving. I am just reporting min max in paper</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3386285D-3D13-374B-A6F3-51FAF5916581}">
   <dimension ref="A1:Y102"/>
@@ -1867,7 +1909,7 @@
         <v>240</v>
       </c>
       <c r="W1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="X1" t="s">
         <v>242</v>
@@ -3637,7 +3679,7 @@
       </c>
       <c r="P29" s="5" cm="1">
         <f t="array" ref="P29">_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 1)</f>
-        <v>71.174000000000007</v>
+        <v>672.25</v>
       </c>
     </row>
     <row r="30" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -3701,7 +3743,7 @@
       </c>
       <c r="P30" s="5" cm="1">
         <f t="array" ref="P30">_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 2)</f>
-        <v>75.647999999999996</v>
+        <v>734.5</v>
       </c>
     </row>
     <row r="31" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -3765,7 +3807,7 @@
       </c>
       <c r="P31" s="5" cm="1">
         <f t="array" ref="P31">_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 3)</f>
-        <v>80.122</v>
+        <v>796.75</v>
       </c>
     </row>
     <row r="32" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -3829,7 +3871,7 @@
       </c>
       <c r="P32" s="5" cm="1">
         <f t="array" ref="P32">_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 3) - _xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 1)</f>
-        <v>8.9479999999999933</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="33" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -3893,7 +3935,7 @@
       </c>
       <c r="P33" s="5" cm="1">
         <f t="array" ref="P33">_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 1) - 1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 3) - _xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 1))</f>
-        <v>57.752000000000017</v>
+        <v>485.5</v>
       </c>
     </row>
     <row r="34" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -3957,7 +3999,7 @@
       </c>
       <c r="P34" s="5" cm="1">
         <f t="array" ref="P34">_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 3) + 1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 3) - _xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""), 1))</f>
-        <v>93.543999999999983</v>
+        <v>983.5</v>
       </c>
     </row>
     <row r="35" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -4021,7 +4063,7 @@
       </c>
       <c r="P35" s="5" cm="1">
         <f t="array" ref="P35">MIN(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""))</f>
-        <v>66.7</v>
+        <v>610</v>
       </c>
     </row>
     <row r="36" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -4085,7 +4127,7 @@
       </c>
       <c r="P36" s="5" cm="1">
         <f t="array" ref="P36">MAX(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000, Fumosimontana!R$2:R1000&lt;&gt;""))</f>
-        <v>84.596000000000004</v>
+        <v>859</v>
       </c>
     </row>
     <row r="37" spans="1:25" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.25">
@@ -4149,7 +4191,7 @@
       </c>
       <c r="P37" s="5" t="str">
         <f>"(" &amp; IF(MIN(Fumosimontana!R$2:R$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)),MIN(Fumosimontana!R$2:R$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!R$2:R$1000, Fumosimontana!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)), Fumosimontana!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!R$2:R$1000, Fumosimontana!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)), Fumosimontana!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!R$2:R$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)),MAX(Fumosimontana!R$2:R$1000),"") &amp; ") mm"</f>
-        <v>() 66.7–84.596 () mm</v>
+        <v>() 610–859 () mm</v>
       </c>
       <c r="Q37" s="5" t="str">
         <f>"(" &amp; IF(MIN(Fumosimontana!S$2:S$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)),MIN(Fumosimontana!S$2:S$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!S$2:S$1000, Fumosimontana!S$2:S$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)), Fumosimontana!S$2:S$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!S$2:S$1000, Fumosimontana!S$2:S$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)), Fumosimontana!S$2:S$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!S$2:S$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!S$2:S$1000,1)),MAX(Fumosimontana!S$2:S$1000),"") &amp; ") mm"</f>
@@ -40688,8 +40730,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2E0072-4AB0-F041-AF4E-7CDA50AF3C1E}">
-  <dimension ref="A1:AH20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2E0072-4AB0-F041-AF4E-7CDA50AF3C1E}">
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -40721,7 +40763,7 @@
     <col min="27" max="27" width="29.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -40803,26 +40845,8 @@
       <c r="AA1" t="s">
         <v>243</v>
       </c>
-      <c r="AC1">
-        <v>4</v>
-      </c>
-      <c r="AD1">
-        <v>11.169</v>
-      </c>
-      <c r="AE1">
-        <v>111.116</v>
-      </c>
-      <c r="AF1">
-        <v>0.878</v>
-      </c>
-      <c r="AG1">
-        <v>251.81299999999999</v>
-      </c>
-      <c r="AH1">
-        <v>116.065</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>99</v>
       </c>
@@ -40896,26 +40920,8 @@
       <c r="AA2">
         <v>3.798</v>
       </c>
-      <c r="AC2">
-        <v>5</v>
-      </c>
-      <c r="AD2">
-        <v>5.5839999999999996</v>
-      </c>
-      <c r="AE2">
-        <v>140.286</v>
-      </c>
-      <c r="AF2">
-        <v>13.148999999999999</v>
-      </c>
-      <c r="AG2">
-        <v>254.10300000000001</v>
-      </c>
-      <c r="AH2">
-        <v>58.048999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>99</v>
       </c>
@@ -40990,7 +40996,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>99</v>
       </c>
@@ -41065,7 +41071,7 @@
         <v>3.6379999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>99</v>
       </c>
@@ -41117,9 +41123,7 @@
       <c r="Q5" s="1">
         <v>16.559999999999999</v>
       </c>
-      <c r="R5" s="1">
-        <v>66.7</v>
-      </c>
+      <c r="R5" s="1"/>
       <c r="S5">
         <v>164.863</v>
       </c>
@@ -41148,7 +41152,7 @@
         <v>2.556</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>99</v>
       </c>
@@ -41226,7 +41230,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>99</v>
       </c>
@@ -41301,7 +41305,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>99</v>
       </c>
@@ -41379,7 +41383,7 @@
         <v>1.7709999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>99</v>
       </c>
@@ -41457,7 +41461,7 @@
         <v>3.0710000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
@@ -41535,7 +41539,7 @@
         <v>3.0430000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>99</v>
       </c>
@@ -41587,9 +41591,7 @@
       <c r="Q11" s="1">
         <v>28.2</v>
       </c>
-      <c r="R11" s="1">
-        <v>84.596000000000004</v>
-      </c>
+      <c r="R11" s="1"/>
       <c r="S11">
         <v>116.065</v>
       </c>
@@ -41612,7 +41614,7 @@
         <v>3.7309999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>99</v>
       </c>
@@ -41687,7 +41689,7 @@
         <v>3.2440000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>99</v>
       </c>
@@ -41757,53 +41759,40 @@
         <v>1.298</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>244</v>
-      </c>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="R14" s="10">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="R15" s="10">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="A17" s="1"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="A18" s="1"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="A19" s="1"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="A20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
